--- a/test/corpus/fixtures/xlsb-binary-workbook-reads-like-its-xlsx-twin/source.xlsx
+++ b/test/corpus/fixtures/xlsb-binary-workbook-reads-like-its-xlsx-twin/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\000023500\dev\ts-xlsx\test\corpus\fixtures\xlsb-binary-workbook-reads-like-its-xlsx-twin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ED2AC6F-9A40-4ACD-B9F4-D766DCE96C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C59ACAF2-F4DF-4EAE-B9A8-F95321C314E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" firstSheet="1" activeTab="2" xr2:uid="{16B9161A-D5A9-4621-84B4-39845C9236C0}"/>
+    <workbookView xWindow="3140" yWindow="3270" windowWidth="14400" windowHeight="8720" firstSheet="1" activeTab="2" xr2:uid="{F2F1B1C4-4F28-46C3-BF1D-AC8BDDDC997A}"/>
   </bookViews>
   <sheets>
     <sheet name="Quiet" sheetId="3" state="hidden" r:id="rId1"/>
@@ -581,7 +581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAC4F7C-2E75-4125-AAAB-89F4C7AAA9D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B32D90-6186-4B51-8B58-7031FEC2BBF7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -591,12 +591,13 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DFB333-8407-49C0-9CC8-8016CFB387C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63A62238-F5D4-469F-AB40-1952940F2044}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
@@ -638,12 +639,13 @@
       <c r="C8" s="11"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="nry3PioCqlEh4CIczWsNqPJsSO6CzeEIY/Zxdmm9l9kUKvC0j6Ftxv5L/Ddjxs+S1Xy96HmgP6V95bHKopsYXg==" saltValue="uq7o93W/PeaNtWE6aZb8BA==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E138AA1E-3574-4448-B7C5-CB874F21714D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB94A640-0389-4221-AFBD-606D08C9394B}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
